--- a/GourmetProject/GameConfig/Datas/__enums_reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_reward.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="19" customWidth="1" style="1" min="2" max="2"/>
@@ -1504,6 +1504,56 @@
       </c>
       <c r="L18" s="0" t="n"/>
     </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RewardPoolSpecialTag</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>奖励池特殊标签</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>BossReward</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Boss奖励池标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ScoreBuild</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>分数构筑标签</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/GourmetProject/GameConfig/Datas/__enums_reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_reward.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e56fe3dc73843c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4deffb996b2840b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1373,6 +1373,66 @@
       </x:c>
       <x:c r="L24"/>
     </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="G25"/>
+      <x:c r="H25" t="str">
+        <x:v>LayWood</x:v>
+      </x:c>
+      <x:c r="I25"/>
+      <x:c r="J25" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>木质铺设道具标签</x:v>
+      </x:c>
+      <x:c r="L25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+      <x:c r="G26"/>
+      <x:c r="H26" t="str">
+        <x:v>LayStone</x:v>
+      </x:c>
+      <x:c r="I26"/>
+      <x:c r="J26" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>石质铺设道具标签</x:v>
+      </x:c>
+      <x:c r="L26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+      <x:c r="G27"/>
+      <x:c r="H27" t="str">
+        <x:v>LayMetal</x:v>
+      </x:c>
+      <x:c r="I27"/>
+      <x:c r="J27" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>金属铺设道具标签</x:v>
+      </x:c>
+      <x:c r="L27"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="H1:L1"/>

--- a/GourmetProject/GameConfig/Datas/__enums_reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_reward.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4deffb996b2840b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R860fdd08257944c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1035,7 +1035,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>通用主动道具</x:v>
+        <x:v>通用消耗品</x:v>
       </x:c>
       <x:c r="L8"/>
     </x:row>
@@ -1073,7 +1073,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>随机强化类主动道具</x:v>
+        <x:v>随机强化类消耗品</x:v>
       </x:c>
       <x:c r="L10"/>
     </x:row>
@@ -1093,7 +1093,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>随机调整类主动道具</x:v>
+        <x:v>随机调整类消耗品</x:v>
       </x:c>
       <x:c r="L11"/>
     </x:row>
@@ -1193,7 +1193,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>强化类主动道具池</x:v>
+        <x:v>强化类消耗品池</x:v>
       </x:c>
       <x:c r="L16"/>
     </x:row>
@@ -1213,7 +1213,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>调整类主动道具池</x:v>
+        <x:v>调整类消耗品池</x:v>
       </x:c>
       <x:c r="L17"/>
     </x:row>
@@ -1241,7 +1241,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>目标分曲线</x:v>
+        <x:v>目标美味值曲线</x:v>
       </x:c>
       <x:c r="L18"/>
     </x:row>
@@ -1261,7 +1261,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>菜品奖励隐藏分</x:v>
+        <x:v>食物奖励隐藏分</x:v>
       </x:c>
       <x:c r="L19"/>
     </x:row>
@@ -1281,7 +1281,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>被动道具奖励隐藏分</x:v>
+        <x:v>装饰品奖励隐藏分</x:v>
       </x:c>
       <x:c r="L20"/>
     </x:row>
@@ -1301,7 +1301,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>餐桌碎片奖励隐藏分</x:v>
+        <x:v>餐桌格奖励隐藏分</x:v>
       </x:c>
       <x:c r="L21"/>
     </x:row>
@@ -1389,7 +1389,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>木质铺设道具标签</x:v>
+        <x:v>木质铺设装饰品和消耗品标签</x:v>
       </x:c>
       <x:c r="L25"/>
     </x:row>
@@ -1409,7 +1409,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>石质铺设道具标签</x:v>
+        <x:v>石质铺设装饰品和消耗品标签</x:v>
       </x:c>
       <x:c r="L26"/>
     </x:row>
@@ -1429,7 +1429,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>金属铺设道具标签</x:v>
+        <x:v>金属铺设装饰品和消耗品标签</x:v>
       </x:c>
       <x:c r="L27"/>
     </x:row>

--- a/GourmetProject/GameConfig/Datas/__enums_reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_reward.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R860fdd08257944c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3cdac00696cf480e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1349,7 +1349,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>Boss奖励池标签</x:v>
+        <x:v>星级评鉴奖励池标签</x:v>
       </x:c>
       <x:c r="L23"/>
     </x:row>
